--- a/artfynd/A 21453-2023 artfynd.xlsx
+++ b/artfynd/A 21453-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21453-2023 artfynd.xlsx
+++ b/artfynd/A 21453-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75553326</v>
+        <v>112529093</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>4188</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örbyhus, Alunda, Upl</t>
+          <t>Koxutmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658617.1735070255</v>
+        <v>658385</v>
       </c>
       <c r="R2" t="n">
-        <v>6676511.070679627</v>
+        <v>6676452</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,29 +754,29 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -775,27 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Håkan Berglund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Sigg</t>
+          <t>Håkan Berglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112529093</v>
+        <v>75553326</v>
       </c>
       <c r="B3" t="n">
-        <v>89114</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,51 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4188</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Koxutmyren, Upl</t>
+          <t>Örbyhus, Alunda, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658386</v>
+        <v>658617</v>
       </c>
       <c r="R3" t="n">
-        <v>6676452</v>
+        <v>6676511</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,29 +861,19 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:27</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:27</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -901,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Berglund</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Berglund</t>
+          <t>Lisa Sigg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 21453-2023 artfynd.xlsx
+++ b/artfynd/A 21453-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529093</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75553326</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>